--- a/需求报工完成分析@20260912.xlsx
+++ b/需求报工完成分析@20260912.xlsx
@@ -1711,7 +1711,7 @@
         <v>46.51</v>
       </c>
       <c r="K14" t="n">
-        <v>31.9</v>
+        <v>3.99</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>10.32</v>
+        <v>1.29</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>26.8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.6</v>
+        <v>1.2</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>7.78</v>
+        <v>0.97</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="K28" t="n">
-        <v>9.960000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>19.71</v>
       </c>
       <c r="K35" t="n">
-        <v>39.01</v>
+        <v>4.88</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>18.6</v>
+        <v>2.33</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>3.11</v>
       </c>
       <c r="K41" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>16.57</v>
       </c>
       <c r="K47" t="n">
-        <v>39.39</v>
+        <v>4.92</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>6.48</v>
       </c>
       <c r="K54" t="n">
-        <v>50.93</v>
+        <v>6.37</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>34.44</v>
       </c>
       <c r="K55" t="n">
-        <v>98.65000000000001</v>
+        <v>12.33</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>35.49</v>
       </c>
       <c r="K56" t="n">
-        <v>86.59999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>36.72</v>
       </c>
       <c r="K62" t="n">
-        <v>57.46</v>
+        <v>7.18</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>10.59</v>
       </c>
       <c r="K66" t="n">
-        <v>123.22</v>
+        <v>15.4</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>12</v>
       </c>
       <c r="K69" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>1.48</v>
       </c>
       <c r="K73" t="n">
-        <v>20.17</v>
+        <v>2.52</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>17.32</v>
       </c>
       <c r="K76" t="n">
-        <v>31.78</v>
+        <v>3.97</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>22.66</v>
       </c>
       <c r="K80" t="n">
-        <v>10.68</v>
+        <v>1.33</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>37</v>
       </c>
       <c r="K82" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43</v>
       </c>
       <c r="K83" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>4</v>
       </c>
       <c r="K95" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>180</v>
+        <v>22.5</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>1.71</v>
       </c>
       <c r="K100" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>4.74</v>
       </c>
       <c r="K104" t="n">
-        <v>157.81</v>
+        <v>19.73</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>14.69</v>
       </c>
       <c r="K108" t="n">
-        <v>2.49</v>
+        <v>0.31</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>364</v>
+        <v>45.5</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>4.83</v>
       </c>
       <c r="K113" t="n">
-        <v>193.35</v>
+        <v>24.17</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>7</v>
       </c>
       <c r="K114" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>17.33</v>
       </c>
       <c r="K115" t="n">
-        <v>53.38</v>
+        <v>6.67</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>9.91</v>
       </c>
       <c r="K117" t="n">
-        <v>59.36</v>
+        <v>7.42</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>3.69</v>
       </c>
       <c r="K118" t="n">
-        <v>39.85</v>
+        <v>4.98</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>0.99</v>
       </c>
       <c r="K119" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>3</v>
       </c>
       <c r="K122" t="n">
-        <v>248</v>
+        <v>31</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>6.32</v>
       </c>
       <c r="K123" t="n">
-        <v>21.47</v>
+        <v>2.68</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>0.37</v>
       </c>
       <c r="K125" t="n">
-        <v>21.03</v>
+        <v>2.63</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>15</v>
       </c>
       <c r="K126" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>8.27</v>
       </c>
       <c r="K128" t="n">
-        <v>365.8</v>
+        <v>45.73</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>17.37</v>
       </c>
       <c r="K134" t="n">
-        <v>135.61</v>
+        <v>16.95</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>3.06</v>
       </c>
       <c r="K135" t="n">
-        <v>360</v>
+        <v>45</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="K136" t="n">
-        <v>349</v>
+        <v>43.62</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>8.02</v>
       </c>
       <c r="K137" t="n">
-        <v>91.78</v>
+        <v>11.47</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>124</v>
+        <v>15.5</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>2.14</v>
       </c>
       <c r="K140" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>2.79</v>
       </c>
       <c r="K141" t="n">
-        <v>33.7</v>
+        <v>4.21</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>13.59</v>
       </c>
       <c r="K145" t="n">
-        <v>39.86</v>
+        <v>4.98</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>35.73</v>
       </c>
       <c r="K149" t="n">
-        <v>122.18</v>
+        <v>15.27</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>6.13</v>
       </c>
       <c r="K152" t="n">
-        <v>101.85</v>
+        <v>12.73</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="n">
-        <v>10.27</v>
+        <v>1.28</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>5.16</v>
       </c>
       <c r="K154" t="n">
-        <v>30.74</v>
+        <v>3.84</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>4.75</v>
       </c>
       <c r="K155" t="n">
-        <v>18</v>
+        <v>2.25</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>16.8</v>
       </c>
       <c r="K159" t="n">
-        <v>19.22</v>
+        <v>2.4</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>0.01</v>
       </c>
       <c r="K162" t="n">
-        <v>71.95</v>
+        <v>8.99</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>2.67</v>
       </c>
       <c r="K163" t="n">
-        <v>10.6</v>
+        <v>1.32</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>3</v>
       </c>
       <c r="K164" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>4.23</v>
       </c>
       <c r="K168" t="n">
-        <v>53.46</v>
+        <v>6.68</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>33.7</v>
       </c>
       <c r="K170" t="n">
-        <v>31.09</v>
+        <v>3.89</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>5.75</v>
       </c>
       <c r="K171" t="n">
-        <v>218</v>
+        <v>27.25</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>0.52</v>
       </c>
       <c r="K173" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>0.03</v>
       </c>
       <c r="K174" t="n">
-        <v>60</v>
+        <v>7.5</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>0.92</v>
       </c>
       <c r="K175" t="n">
-        <v>24.65</v>
+        <v>3.08</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>0.64</v>
       </c>
       <c r="K178" t="n">
-        <v>146.9</v>
+        <v>18.36</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>0.72</v>
       </c>
       <c r="K180" t="n">
-        <v>10.23</v>
+        <v>1.28</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>16.62</v>
       </c>
       <c r="K181" t="n">
-        <v>134</v>
+        <v>16.75</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>15.5</v>
       </c>
       <c r="K182" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>39.71</v>
       </c>
       <c r="K183" t="n">
-        <v>74.3</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>10.83</v>
       </c>
       <c r="K184" t="n">
-        <v>57.35</v>
+        <v>7.17</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>47</v>
       </c>
       <c r="K186" t="n">
-        <v>8.24</v>
+        <v>1.03</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>8.34</v>
       </c>
       <c r="K187" t="n">
-        <v>306.17</v>
+        <v>38.27</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>4.42</v>
+        <v>0.55</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>8.01</v>
       </c>
       <c r="K189" t="n">
-        <v>74.40000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>5.74</v>
       </c>
       <c r="K190" t="n">
-        <v>32.49</v>
+        <v>4.06</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>3.6</v>
       </c>
       <c r="K192" t="n">
-        <v>59.18</v>
+        <v>7.4</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>7.03</v>
       </c>
       <c r="K195" t="n">
-        <v>251.1</v>
+        <v>31.39</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="K196" t="n">
-        <v>89.59999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>0.53</v>
       </c>
       <c r="K198" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>11.1</v>
       </c>
       <c r="K202" t="n">
-        <v>65.76000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>1.52</v>
       </c>
       <c r="K203" t="n">
-        <v>67.81999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>22</v>
       </c>
       <c r="K204" t="n">
-        <v>9.800000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>3.62</v>
       </c>
       <c r="K205" t="n">
-        <v>207</v>
+        <v>25.88</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>9.59</v>
       </c>
       <c r="K206" t="n">
-        <v>335.61</v>
+        <v>41.95</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>5.02</v>
       </c>
       <c r="K208" t="n">
-        <v>153.85</v>
+        <v>19.23</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>2.35</v>
       </c>
       <c r="K211" t="n">
-        <v>55.59</v>
+        <v>6.95</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>4.54</v>
       </c>
       <c r="K212" t="n">
-        <v>19.66</v>
+        <v>2.46</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>4</v>
       </c>
       <c r="K213" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>26.75</v>
       </c>
       <c r="K214" t="n">
-        <v>90</v>
+        <v>11.25</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>11.5</v>
       </c>
       <c r="K219" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>0.25</v>
       </c>
       <c r="K221" t="n">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>9.25</v>
       </c>
       <c r="K222" t="n">
-        <v>334</v>
+        <v>41.75</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>296</v>
+        <v>37</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>260</v>
+        <v>32.5</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>1</v>
       </c>
       <c r="K225" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>6.59</v>
       </c>
       <c r="K227" t="n">
-        <v>243.22</v>
+        <v>30.4</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>4.25</v>
       </c>
       <c r="K228" t="n">
-        <v>293.99</v>
+        <v>36.75</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>82.13</v>
+        <v>10.27</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>98.61</v>
+        <v>12.33</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>326.63</v>
+        <v>40.83</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>7.44</v>
       </c>
       <c r="K237" t="n">
-        <v>148</v>
+        <v>18.5</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>8.83</v>
       </c>
       <c r="K238" t="n">
-        <v>283.56</v>
+        <v>35.45</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>239.65</v>
+        <v>29.96</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>5.38</v>
       </c>
       <c r="K240" t="n">
-        <v>71.97</v>
+        <v>9</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="K241" t="n">
-        <v>60.89</v>
+        <v>7.61</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>71.48999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>84</v>
+        <v>10.5</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>1.31</v>
       </c>
       <c r="K244" t="n">
-        <v>51.73</v>
+        <v>6.47</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>0.25</v>
       </c>
       <c r="K245" t="n">
-        <v>30</v>
+        <v>3.75</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>0.48</v>
       </c>
       <c r="K246" t="n">
-        <v>22.82</v>
+        <v>2.85</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>117.26</v>
+        <v>14.66</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>6.99</v>
       </c>
       <c r="K248" t="n">
-        <v>10.33</v>
+        <v>1.29</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="n">
-        <v>284.3</v>
+        <v>35.54</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>264</v>
+        <v>33</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>25.64</v>
       </c>
       <c r="K254" t="n">
-        <v>90.89</v>
+        <v>11.36</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>34</v>
+        <v>4.25</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>1</v>
       </c>
       <c r="K258" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>0.66</v>
       </c>
       <c r="K260" t="n">
-        <v>42.7</v>
+        <v>5.34</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>0.03</v>
       </c>
       <c r="K263" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>15</v>
       </c>
       <c r="K265" t="n">
-        <v>125.9</v>
+        <v>15.74</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>0.57</v>
       </c>
       <c r="K266" t="n">
-        <v>19.41</v>
+        <v>2.43</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>0.96</v>
       </c>
       <c r="K267" t="n">
-        <v>133.72</v>
+        <v>16.71</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>303.63</v>
+        <v>37.95</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>31</v>
       </c>
       <c r="K272" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>2.95</v>
       </c>
       <c r="K274" t="n">
-        <v>109.85</v>
+        <v>13.73</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>72.75</v>
+        <v>9.09</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>0.21</v>
       </c>
       <c r="K277" t="n">
-        <v>70.03</v>
+        <v>8.75</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>176.7</v>
+        <v>22.09</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="K279" t="n">
-        <v>475.38</v>
+        <v>59.42</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>67.84</v>
+        <v>8.48</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>0.26</v>
       </c>
       <c r="K281" t="n">
-        <v>326.05</v>
+        <v>40.76</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>0.01</v>
       </c>
       <c r="K282" t="n">
-        <v>123.11</v>
+        <v>15.39</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>2.5</v>
       </c>
       <c r="K283" t="n">
-        <v>93</v>
+        <v>11.62</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>1.7</v>
       </c>
       <c r="K285" t="n">
-        <v>58.39</v>
+        <v>7.3</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>43.5</v>
       </c>
       <c r="K286" t="n">
-        <v>76.02</v>
+        <v>9.5</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>8.470000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>294</v>
+        <v>36.75</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>187.4</v>
+        <v>23.43</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>6</v>
+        <v>0.75</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>6.75</v>
       </c>
       <c r="K295" t="n">
-        <v>50</v>
+        <v>6.25</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>0.55</v>
       </c>
       <c r="K297" t="n">
-        <v>19.58</v>
+        <v>2.45</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>12.58</v>
       </c>
       <c r="K299" t="n">
-        <v>99.39</v>
+        <v>12.42</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>38.02</v>
+        <v>4.75</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>0</v>
       </c>
       <c r="K302" t="n">
-        <v>44</v>
+        <v>5.5</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>27.82</v>
+        <v>3.48</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>0</v>
       </c>
       <c r="K304" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>62.33</v>
+        <v>7.79</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>1.6</v>
       </c>
       <c r="K307" t="n">
-        <v>211.19</v>
+        <v>26.4</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>0.24</v>
       </c>
       <c r="K309" t="n">
-        <v>22.1</v>
+        <v>2.76</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>5.57</v>
       </c>
       <c r="K313" t="n">
-        <v>115.56</v>
+        <v>14.45</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>122.26</v>
+        <v>15.28</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>1.15</v>
       </c>
       <c r="K319" t="n">
-        <v>53.25</v>
+        <v>6.66</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>0.88</v>
       </c>
       <c r="K321" t="n">
-        <v>33</v>
+        <v>4.12</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>0.25</v>
       </c>
       <c r="K323" t="n">
-        <v>38</v>
+        <v>4.75</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>35.75</v>
       </c>
       <c r="K332" t="n">
-        <v>90</v>
+        <v>11.25</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>136.56</v>
+        <v>17.07</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>308</v>
+        <v>38.5</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>0.84</v>
       </c>
       <c r="K336" t="n">
-        <v>25.29</v>
+        <v>3.16</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>313.07</v>
+        <v>39.13</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>3.85</v>
       </c>
       <c r="K339" t="n">
-        <v>18.5</v>
+        <v>2.31</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>2.87</v>
+        <v>0.36</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>40.98</v>
       </c>
       <c r="K341" t="n">
-        <v>93.47</v>
+        <v>11.68</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>30.79</v>
+        <v>3.85</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>25.61</v>
       </c>
       <c r="K348" t="n">
-        <v>181.14</v>
+        <v>22.64</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>0.2</v>
       </c>
       <c r="K350" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>2.58</v>
       </c>
       <c r="K351" t="n">
-        <v>131.36</v>
+        <v>16.42</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>0.99</v>
       </c>
       <c r="K353" t="n">
-        <v>36.11</v>
+        <v>4.51</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>1.85</v>
       </c>
       <c r="K354" t="n">
-        <v>109.62</v>
+        <v>13.7</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>3.79</v>
+        <v>0.47</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>2.15</v>
       </c>
       <c r="K356" t="n">
-        <v>56.1</v>
+        <v>7.01</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>53.72</v>
+        <v>6.71</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>0.5</v>
       </c>
       <c r="K363" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>0.01</v>
       </c>
       <c r="K365" t="n">
-        <v>19</v>
+        <v>2.38</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>3</v>
       </c>
       <c r="K366" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>2.88</v>
       </c>
       <c r="K368" t="n">
-        <v>217</v>
+        <v>27.12</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>164</v>
+        <v>20.5</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>122.9</v>
+        <v>15.36</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>1.34</v>
       </c>
       <c r="K377" t="n">
-        <v>31.27</v>
+        <v>3.91</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>0.57</v>
       </c>
       <c r="K382" t="n">
-        <v>19.43</v>
+        <v>2.43</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>0.04</v>
       </c>
       <c r="K383" t="n">
-        <v>11.67</v>
+        <v>1.46</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>3</v>
       </c>
       <c r="K389" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>42.17</v>
       </c>
       <c r="K390" t="n">
-        <v>74.67</v>
+        <v>9.33</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
-        <v>33</v>
+        <v>4.12</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>0</v>
       </c>
       <c r="K398" t="n">
-        <v>2.63</v>
+        <v>0.33</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>12.5</v>
       </c>
       <c r="K400" t="n">
-        <v>172.04</v>
+        <v>21.5</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>33.5</v>
       </c>
       <c r="K401" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>0</v>
       </c>
       <c r="K405" t="n">
-        <v>271.67</v>
+        <v>33.96</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>9.67</v>
       </c>
       <c r="K408" t="n">
-        <v>172.79</v>
+        <v>21.6</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>3.35</v>
       </c>
       <c r="K411" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>0.05</v>
       </c>
       <c r="K416" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>0</v>
       </c>
       <c r="K417" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>7.11</v>
       </c>
       <c r="K420" t="n">
-        <v>175.12</v>
+        <v>21.89</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>6.55</v>
       </c>
       <c r="K421" t="n">
-        <v>211.6</v>
+        <v>26.45</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>0</v>
       </c>
       <c r="K429" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>20.02</v>
       </c>
       <c r="K431" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>24.75</v>
       </c>
       <c r="K434" t="n">
-        <v>136.31</v>
+        <v>17.04</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>0</v>
       </c>
       <c r="K437" t="n">
-        <v>23.6</v>
+        <v>2.95</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>21.25</v>
       </c>
       <c r="K439" t="n">
-        <v>375.01</v>
+        <v>46.88</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>0</v>
       </c>
       <c r="K442" t="n">
-        <v>17.82</v>
+        <v>2.23</v>
       </c>
       <c r="L442" t="inlineStr">
         <is>
